--- a/data/trans_orig/IP16A09-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16A09-Provincia-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>507</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7889</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18922</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23292</t>
+          <t>23296</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>620</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>13671</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15242</t>
+          <t>15175</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19856</t>
+          <t>19236</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31269</t>
+          <t>30837</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35957</t>
+          <t>35925</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13065</t>
+          <t>12671</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28988</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18167</t>
+          <t>18184</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23243</t>
+          <t>22693</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>44040</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>448</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>4530</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>447</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5668</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20962</t>
+          <t>21394</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25480</t>
+          <t>25476</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>60122</t>
+          <t>60588</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>65341</t>
+          <t>65343</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>7196</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14346</t>
+          <t>13572</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>116111</t>
+          <t>115866</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>123039</t>
+          <t>122929</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>136135</t>
+          <t>136723</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>142627</t>
+          <t>142631</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>254878</t>
+          <t>255652</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>264326</t>
+          <t>264403</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16419</t>
+          <t>16364</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41045</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>626</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28958</t>
+          <t>28396</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33510</t>
+          <t>32784</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>64549</t>
+          <t>64466</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69613</t>
+          <t>69615</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14837</t>
+          <t>15965</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20204</t>
+          <t>20402</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38251</t>
+          <t>37637</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2696</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10891</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30080</t>
+          <t>29465</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28604</t>
+          <t>28916</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25121</t>
+          <t>25008</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>56471</t>
+          <t>56280</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>62053</t>
+          <t>62046</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5569</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21584</t>
+          <t>21335</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>45744</t>
+          <t>46356</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>7573</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15211</t>
+          <t>14812</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>178321</t>
+          <t>179419</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>185854</t>
+          <t>185759</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>180873</t>
+          <t>180978</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>188838</t>
+          <t>188985</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>363259</t>
+          <t>363658</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>373367</t>
+          <t>373604</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16795</t>
+          <t>16879</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41262</t>
+          <t>41431</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>701</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16564</t>
+          <t>17241</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21999</t>
+          <t>22613</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47310</t>
+          <t>47185</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53021</t>
+          <t>53030</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4268</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30647</t>
+          <t>30736</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60524</t>
+          <t>60613</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16526</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30520</t>
+          <t>30612</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>570</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2391</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>9879</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>157406</t>
+          <t>156684</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>161969</t>
+          <t>161966</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>141737</t>
+          <t>141108</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>147422</t>
+          <t>147418</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>301701</t>
+          <t>300782</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>308416</t>
+          <t>308270</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A09-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16A09-Provincia-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3522</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>29,02%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1034</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2782</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3216</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,86%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>23,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3537</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>505</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11450</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8613</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>70,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>10634</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8886</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8452</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>11668</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>91,14%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>76,16%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>72,44%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>11450</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>8598</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,35%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>70,85%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>33</t>
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>19051</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23296</t>
+          <t>23298</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12135</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>11668</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>11668</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>11668</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12135</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1937</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4620</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>23,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>613</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3059</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3482</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,66%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1937</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4681</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,75%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17919</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15236</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>19228</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,25%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>76,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,84%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>16117</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13671</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>13248</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>16730</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,34%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>81,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>79,19%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>17919</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>15175</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>19236</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,25%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>76,43%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>96,88%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>53</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30837</t>
+          <t>30863</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35925</t>
+          <t>35944</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>16730</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>16730</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>16730</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>19856</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>11627</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11627</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>11627</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>11627</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>10561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1047</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3680</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,4%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22,51%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>20,93%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3234</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1047</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3714</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>15304</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12671</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>12929</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>16351</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>93,6%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>77,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>79,07%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>45</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>29543</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>16426</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>16351</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>16351</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>16351</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>16426</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2207,47 +2207,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>9126</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7820</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>9126</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>9126</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>9126</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7820</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>12379</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>10729</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>12379</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>12379</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>12379</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2785,102 +2785,102 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>12,45%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>665</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3315</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3115</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>3,1%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>15,42%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>14,49%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3833</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>4640</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>14,45%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1315</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3985</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -2893,74 +2893,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>25876</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>23223</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>87,55%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>20834</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>18184</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>18384</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>21499</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>96,9%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>84,58%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>85,51%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>25876</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>22693</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>85,55%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>67</t>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>44040</t>
+          <t>43385</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>26526</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>21499</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>21499</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>21499</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3123,72 +3123,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>1838</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>448</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>4530</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5348</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>7,09%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>17,47%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -3236,72 +3236,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>24086</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>21394</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>25476</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>20576</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>25472</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>92,91%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>82,53%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>60588</t>
+          <t>60926</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3349,57 +3349,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>39867</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>25924</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>25924</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>25924</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>39867</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3466,72 +3466,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>7416</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>5197</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>9439</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>2528</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>9976</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>4,15%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>3272</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>1288</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>7196</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13572</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -3579,72 +3579,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>140647</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>136503</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>142637</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>97,73%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>94,85%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>120108</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>115866</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>122929</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>115329</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>122777</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>95,85%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>92,47%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>140647</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>136723</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>142631</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>97,73%</t>
-        </is>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>255652</t>
+          <t>255911</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>264403</t>
+          <t>264678</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -3692,57 +3692,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3877,7 +3877,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4045,107 +4045,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>498</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2696</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2424</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,61%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2608</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>498</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2545</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -4158,74 +4158,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24583</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18562</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16364</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16636</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>19060</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,39%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>85,85%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>87,28%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24583</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>60</t>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>41036</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4271,57 +4271,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24583</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24583</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24583</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>19060</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>19060</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>19060</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24583</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24583</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24583</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4393,67 +4393,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4445</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1272</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4551</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4508</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,86%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,81%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1235</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4510</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -4501,74 +4501,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>36059</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32849</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>37294</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,69%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,08%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>31675</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>28396</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>28439</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>32947</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,14%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>86,32%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>36059</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>32784</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>37294</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,69%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>87,91%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>101</t>
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>64466</t>
+          <t>64424</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69615</t>
+          <t>69614</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4614,57 +4614,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>37294</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>37294</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>37294</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>32947</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>32947</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>32947</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>37294</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>37294</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>37294</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4736,102 +4736,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3023</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,78%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>787</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3311</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3362</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,08%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,17%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>17,44%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1531</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3256</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4749</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>13,76%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1531</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5297</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -4844,74 +4844,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>22914</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>20635</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>23658</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,85%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,22%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>18489</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>15965</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>15914</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>19276</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,92%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>82,83%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>82,56%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>22914</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>20402</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>23658</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,85%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>86,24%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>58</t>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37637</t>
+          <t>38185</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4957,57 +4957,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23658</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>23658</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23658</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>19276</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>19276</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>19276</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>23658</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>23658</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>23658</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5187,47 +5187,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>24892</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>16750</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5300,57 +5300,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>24892</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>24892</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>24892</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>16750</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>16750</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>16750</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5417,107 +5417,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3384</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>24,9%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>647</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3407</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3767</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>25,08%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3935</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -5530,72 +5530,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12940</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>13587</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,24%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>75,1%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>19813</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>12940</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>10180</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>13587</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,24%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29465</t>
+          <t>29633</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5643,57 +5643,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>13587</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13587</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13587</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>19813</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>19813</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>19813</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>13587</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>13587</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>13587</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5873,47 +5873,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>19510</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>13142</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>19510</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5986,57 +5986,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>19510</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>19510</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>19510</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>13142</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>13142</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>13142</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>19510</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>19510</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>19510</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6103,72 +6103,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4016</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>13,76%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4595</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5423</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>2,82%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>13,71%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4183</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -6216,74 +6216,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>27874</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>25175</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>29191</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>95,49%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>86,24%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>32567</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>28916</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>28088</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>33511</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>97,18%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>86,29%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>83,82%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>27874</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>25008</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>29191</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>95,49%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>85,67%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>85</t>
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>56280</t>
+          <t>56549</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>62046</t>
+          <t>62057</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -6329,57 +6329,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>29191</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>29191</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>29191</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>33511</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>33511</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>33511</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>29191</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>29191</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>29191</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6446,107 +6446,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4967</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>18,46%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>1639</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>5569</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>5468</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>20,7%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1639</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>4899</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -6564,67 +6564,67 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>25265</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>21937</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>26904</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>93,91%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>81,54%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>24350</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>25265</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>21335</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>26904</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>93,91%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>46356</t>
+          <t>45787</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6672,57 +6672,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>26904</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>26904</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>26904</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>24350</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>24350</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>24350</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>26904</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>26904</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>26904</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6789,72 +6789,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>5582</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2611</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>10721</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>3501</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>1233</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>7573</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>1267</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>1,87%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>5582</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>2493</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>10500</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>15444</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -6902,72 +6902,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>185896</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>180757</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>188867</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>97,08%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>94,4%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>98,64%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>183491</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>179419</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>185759</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>179223</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>185725</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>98,13%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>95,95%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>185896</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>180978</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>188985</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>97,08%</t>
-        </is>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>363658</t>
+          <t>363026</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>373604</t>
+          <t>373364</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -7015,57 +7015,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>186992</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7200,7 +7200,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7368,107 +7368,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>540</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2676</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2332</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,76%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>11,93%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2625</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -7481,74 +7481,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24501</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>19015</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16879</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17223</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>19555</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,24%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>86,32%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>88,07%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24501</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>64</t>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41431</t>
+          <t>40874</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7594,57 +7594,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24501</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24501</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24501</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>19555</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>19555</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>19555</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24501</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24501</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24501</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7711,92 +7711,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6701</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>2799</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6077</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>12,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>26,06%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2799</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>710</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -7824,72 +7824,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20519</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16617</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>22591</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>88,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>71,26%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>30413</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>20519</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>17241</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>22613</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>88,0%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47185</t>
+          <t>46872</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53030</t>
+          <t>53021</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -7937,57 +7937,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>23318</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>23318</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>23318</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>30413</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>30413</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>30413</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>23318</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>23318</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>23318</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8167,47 +8167,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9727</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>10287</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>9727</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -8280,57 +8280,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9727</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9727</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9727</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>10287</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>10287</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>10287</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>9727</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9727</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>9727</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8397,107 +8397,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1124</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4179</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3906</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,22%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,97%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>11,19%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1124</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4006</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1124</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3914</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -8510,74 +8510,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29612</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>33791</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>30736</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>31009</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>34915</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,78%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,03%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>88,81%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>29612</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>89</t>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60613</t>
+          <t>60521</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8623,57 +8623,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>29612</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>29612</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>29612</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>34915</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>34915</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>34915</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>29612</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>29612</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>29612</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8858,42 +8858,42 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>7262</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>7779</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>7262</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -8971,52 +8971,52 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>7262</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7262</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7262</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>7779</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>7779</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>7779</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>7262</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>7262</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7262</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9196,47 +9196,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9475</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>10580</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>9475</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -9309,57 +9309,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>9475</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>9475</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>9475</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>10580</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>10580</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>10580</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>9475</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>9475</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>9475</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9426,107 +9426,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>613</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3102</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3089</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>3,11%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>15,73%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>15,67%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3511</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3065</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -9539,74 +9539,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>19100</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>16611</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>16624</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>19713</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>96,89%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>84,27%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>84,33%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>13964</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>50</t>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30612</t>
+          <t>30166</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9652,57 +9652,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>19713</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>19713</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>19713</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>13964</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>13964</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>13964</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9882,47 +9882,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>30267</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>29294</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>30267</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -9995,57 +9995,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>30267</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>30267</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>30267</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>29294</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>29294</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>29294</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>30267</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>30267</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>30267</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10117,67 +10117,67 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>6921</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
           <t>2277</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5852</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5948</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>2799</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>7017</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2391</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9879</t>
+          <t>9767</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -10225,74 +10225,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>145326</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>141204</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>147420</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>98,11%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>95,33%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>160259</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>156684</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>161966</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>156588</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>161965</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>98,6%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>96,4%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>96,34%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>99,65%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>145326</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>141108</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>147418</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>452</t>
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>300782</t>
+          <t>300894</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>308270</t>
+          <t>308356</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -10338,57 +10338,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>162536</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
